--- a/Deliverables/final.xlsx
+++ b/Deliverables/final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Frameworks\Capstone\Deliverables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B7BDB5C8-389F-4F4E-A8FB-EF7D5A9B234A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14CB57EF-BCE6-4FE7-B2F7-618346EF317D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="506">
   <si>
     <t>PARABANK ROBOT FRAMEWORK CAPSTONE — MANUAL TEST PLAN</t>
   </si>
@@ -457,12 +457,6 @@
     <t>'Transfer Complete!' heading visible; amount reflects entered value</t>
   </si>
   <si>
-    <t>TC-LOAN-01</t>
-  </si>
-  <si>
-    <t>Apply for Loan Using Valid Account</t>
-  </si>
-  <si>
     <t>TC-NEG-UI-01</t>
   </si>
   <si>
@@ -506,9 +500,6 @@
   </si>
   <si>
     <t>Validation error shown; zero-amount transfer rejected</t>
-  </si>
-  <si>
-    <t>TC-NEG-UI-04</t>
   </si>
   <si>
     <t>TC-API-01</t>
@@ -1083,18 +1074,12 @@
     <t>Transfer to Same Account – Should Be Rejected</t>
   </si>
   <si>
-    <t>DEF-IMPL-01</t>
-  </si>
-  <si>
     <t>Transfer with Negative Amount – Should Be Rejected</t>
   </si>
   <si>
     <t>Transfer with Zero Amount – Should Be Rejected</t>
   </si>
   <si>
-    <t>Protected Page Redirects Without Login Session</t>
-  </si>
-  <si>
     <t>api, smoke</t>
   </si>
   <si>
@@ -1140,9 +1125,6 @@
     <t>performance</t>
   </si>
   <si>
-    <t>20 Concurrent API Requests All Return 200</t>
-  </si>
-  <si>
     <t>DEFECT REPORT — ParaBank Robot Framework Capstone</t>
   </si>
   <si>
@@ -1159,9 +1141,6 @@
   </si>
   <si>
     <t>DEF-001</t>
-  </si>
-  <si>
-    <t>Negative Amount Transfer Is Accepted Without Validation</t>
   </si>
   <si>
     <t>1. Login
@@ -1174,16 +1153,10 @@
     <t>Validation error: 'Amount must be greater than zero'</t>
   </si>
   <si>
-    <t>Transfer completes with negative amount — no error shown</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
     <t>DEF-002</t>
-  </si>
-  <si>
-    <t>Zero Amount Transfer Is Accepted Without Validation</t>
   </si>
   <si>
     <t>1. Login
@@ -1218,15 +1191,6 @@
     <t>DEF-004</t>
   </si>
   <si>
-    <t>DEF-005</t>
-  </si>
-  <si>
-    <t>DEF-006</t>
-  </si>
-  <si>
-    <t>DEF-007</t>
-  </si>
-  <si>
     <t>FINAL TEST SUMMARY REPORT — ParaBank Robot Framework Capstone</t>
   </si>
   <si>
@@ -1477,177 +1441,6 @@
   </si>
   <si>
     <t>'Transfer Complete!'</t>
-  </si>
-  <si>
-    <t>TC-UCI-01</t>
-  </si>
-  <si>
-    <t>Update Contact Info Accepts Numbers/Special Characters in First Name, Last Name, City and State Fields</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Update Contact Info3. Enter values like John123, Jaipur@, Raj#sthan, Doe4564. Save changes"</t>
-  </si>
-  <si>
-    <t>Only alphabetic characters should be accepted in First Name, Last Name, City and State fields</t>
-  </si>
-  <si>
-    <t>Form accepts numeric and special character values without validation</t>
-  </si>
-  <si>
-    <t>TC-UCI-02</t>
-  </si>
-  <si>
-    <t>Update Contact Info Accepts Alphabets/Special Characters in Zip Code Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Update Contact Info3. Enter Zip Code: ABC12@4. Save changes"</t>
-  </si>
-  <si>
-    <t>Zip Code should accept numeric values only</t>
-  </si>
-  <si>
-    <t>Alphabetic and special characters are accepted</t>
-  </si>
-  <si>
-    <t>TC-UCI-03</t>
-  </si>
-  <si>
-    <t>Update Contact Info Accepts Alphabets/Special Characters in SSN Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Update Contact Info3. Enter SSN: ABC@1234. Save changes"</t>
-  </si>
-  <si>
-    <t>SSN should accept numeric values only in valid format</t>
-  </si>
-  <si>
-    <t>Invalid alphabetic and special character values are accepted</t>
-  </si>
-  <si>
-    <t>TC-UCI-04</t>
-  </si>
-  <si>
-    <t>Update Contact Info Accepts Alphabets/Special Characters in Phone Number Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Update Contact Info3. Enter Phone Number: ABC123@#4. Save changes"</t>
-  </si>
-  <si>
-    <t>Phone Number should accept numeric values only</t>
-  </si>
-  <si>
-    <t>Invalid phone number containing alphabets and special characters is accepted</t>
-  </si>
-  <si>
-    <t>DEF-008</t>
-  </si>
-  <si>
-    <t>TC-BP-01</t>
-  </si>
-  <si>
-    <t>Bill Pay Accepts Numbers/Special Characters in First Name, Last Name, City and State Fields</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Bill Pay3. Enter values such as John123, Jaipur@, Doe456, Raj#sthan4. Submit payment"</t>
-  </si>
-  <si>
-    <t>First Name, Last Name, City and State should accept only alphabetic values</t>
-  </si>
-  <si>
-    <t>Invalid values containing numbers and special characters are accepted</t>
-  </si>
-  <si>
-    <t>DEF-009</t>
-  </si>
-  <si>
-    <t>TC-BP-02</t>
-  </si>
-  <si>
-    <t>Bill Pay Accepts Alphabets/Special Characters in Zip Code Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Bill Pay3. Enter Zip Code: ABC12@4. Submit payment"</t>
-  </si>
-  <si>
-    <t>Zip Code should contain only numeric values</t>
-  </si>
-  <si>
-    <t>Invalid Zip Code is accepted without validation</t>
-  </si>
-  <si>
-    <t>DEF-010</t>
-  </si>
-  <si>
-    <t>TC-BP-03</t>
-  </si>
-  <si>
-    <t>Bill Pay Accepts Alphabets/Special Characters in Phone Number Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Bill Pay3. Enter Phone Number: ABC123@#4. Submit payment"</t>
-  </si>
-  <si>
-    <t>Phone Number should accept only numeric values</t>
-  </si>
-  <si>
-    <t>Invalid phone number is accepted</t>
-  </si>
-  <si>
-    <t>DEF-011</t>
-  </si>
-  <si>
-    <t>TC-BP-04</t>
-  </si>
-  <si>
-    <t>Bill Pay Accepts Alphabets/Special Characters in Account Number Field</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Bill Pay3. Enter Account Number: ACC123@#4. Submit payment"</t>
-  </si>
-  <si>
-    <t>Account Number should contain only numeric values</t>
-  </si>
-  <si>
-    <t>Alphabetic and special character values are accepted</t>
-  </si>
-  <si>
-    <t>DEF-012</t>
-  </si>
-  <si>
-    <t>TC-FT-01</t>
-  </si>
-  <si>
-    <t>Find Transactions Accepts Invalid Date Format</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Find Transactions3. Select Search by Date4. Enter date: 17-06-20265. Click Find Transactions"</t>
-  </si>
-  <si>
-    <t>Application should validate date format and display error message</t>
-  </si>
-  <si>
-    <t>Search executes successfully or accepts invalid date format without validation</t>
-  </si>
-  <si>
-    <t>DEF-013</t>
-  </si>
-  <si>
-    <t>TC-FT-02</t>
-  </si>
-  <si>
-    <t>Find Transactions Accepts Non-Existent Date</t>
-  </si>
-  <si>
-    <t>"1. Login2. Navigate to Find Transactions3. Enter date: 31/02/20264. Click Find Transactions"</t>
-  </si>
-  <si>
-    <t>Validation message should be displayed for invalid calendar date</t>
-  </si>
-  <si>
-    <t>System accepts invalid date and processes request</t>
-  </si>
-  <si>
-    <t>Transfer Amount Greater Than The Balance</t>
   </si>
   <si>
     <t>Register User with Password and Confirm Password Mismatch</t>
@@ -1875,6 +1668,33 @@
   </si>
   <si>
     <t>TC-LGN-01, TC-NEG-LGN-02, TC-NEG-LGN-03, TC-LGN-04, TC-API-01, TC-NEG-TF-02, TC-NEG-TF-03, TC-NEG-TF-04, TC-NEG-TF-05</t>
+  </si>
+  <si>
+    <t>Amount Greater Than the Account Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Amount Transfer </t>
+  </si>
+  <si>
+    <t>Negative Amount Transfer</t>
+  </si>
+  <si>
+    <t>Validation error: 'Amount can't be greater than the account balance'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer completes — and the balance of the source account is negative </t>
+  </si>
+  <si>
+    <t>Transfer completes with negative amount — no error shown and reverse transaction occurs</t>
+  </si>
+  <si>
+    <t>5 Concurrent API Requests All Return 200</t>
+  </si>
+  <si>
+    <t>Transfer Amount Greater Than The Balance – Should Be Rejected</t>
+  </si>
+  <si>
+    <t>defect</t>
   </si>
 </sst>
 </file>
@@ -2034,7 +1854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2090,9 +1910,6 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2113,6 +1930,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2430,10 +2253,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
+      <c r="B1" s="25"/>
     </row>
     <row r="2" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2570,184 +2393,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>518</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>519</v>
-      </c>
-      <c r="D3" s="24" t="s">
+      <c r="B3" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>520</v>
+      <c r="E3" s="23" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>521</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>522</v>
-      </c>
-      <c r="D4" s="24" t="s">
+      <c r="B4" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>453</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="24" t="s">
-        <v>523</v>
+      <c r="E4" s="23" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>524</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>525</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="B5" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>520</v>
+      <c r="E5" s="23" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>526</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>527</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>528</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>529</v>
+      <c r="B6" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>530</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>531</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>532</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>523</v>
+      <c r="B7" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>533</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>534</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="B8" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>535</v>
+      <c r="E8" s="23" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="24" t="s">
-        <v>536</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>537</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>538</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>539</v>
+      <c r="B9" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>540</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>541</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>528</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>542</v>
+      <c r="B10" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>543</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>544</v>
-      </c>
-      <c r="D11" s="24" t="s">
+      <c r="B11" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="24" t="s">
-        <v>325</v>
+      <c r="E11" s="23" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2774,18 +2597,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -2810,7 +2633,7 @@
         <v>86</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>33</v>
@@ -2853,13 +2676,13 @@
     </row>
     <row r="4" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>506</v>
+        <v>437</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>493</v>
+        <v>424</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>37</v>
@@ -2868,13 +2691,13 @@
         <v>90</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>496</v>
+        <v>427</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>497</v>
+        <v>428</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>497</v>
+        <v>428</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>36</v>
@@ -2885,13 +2708,13 @@
     </row>
     <row r="5" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>507</v>
+        <v>438</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>494</v>
+        <v>425</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>37</v>
@@ -2900,13 +2723,13 @@
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>498</v>
+        <v>429</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>499</v>
+        <v>430</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>36</v>
@@ -2917,13 +2740,13 @@
     </row>
     <row r="6" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>495</v>
+        <v>426</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>37</v>
@@ -2932,13 +2755,13 @@
         <v>90</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>500</v>
+        <v>431</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>501</v>
+        <v>432</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>501</v>
+        <v>432</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>36</v>
@@ -2981,7 +2804,7 @@
     </row>
     <row r="8" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>510</v>
+        <v>441</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>46</v>
@@ -3013,7 +2836,7 @@
     </row>
     <row r="9" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>511</v>
+        <v>442</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>47</v>
@@ -3141,7 +2964,7 @@
     </row>
     <row r="13" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>514</v>
+        <v>445</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>51</v>
@@ -3172,157 +2995,157 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="51" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>512</v>
-      </c>
-      <c r="B14" s="20" t="s">
+      <c r="A14" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>492</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="C14" s="20" t="s">
+        <v>504</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>517</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>434</v>
-      </c>
-      <c r="I14" s="20" t="s">
+      <c r="H15" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="I15" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="51" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="D15" s="20" t="s">
+      <c r="J15" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>434</v>
-      </c>
-      <c r="I15" s="20" t="s">
+      <c r="E16" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="J15" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="51" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>515</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="J16" s="17" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="51" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="21" t="s">
+      <c r="E17" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H16" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="I16" s="20" t="s">
+      <c r="G17" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="J16" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="51" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>516</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="H17" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>74</v>
-      </c>
       <c r="J17" s="17" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>45</v>
@@ -3333,28 +3156,28 @@
     </row>
     <row r="19" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>57</v>
@@ -3365,28 +3188,28 @@
     </row>
     <row r="20" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>59</v>
@@ -3397,28 +3220,28 @@
     </row>
     <row r="21" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>57</v>
@@ -3429,28 +3252,28 @@
     </row>
     <row r="22" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>36</v>
@@ -3461,28 +3284,28 @@
     </row>
     <row r="23" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>36</v>
@@ -3493,28 +3316,28 @@
     </row>
     <row r="24" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>36</v>
@@ -3525,7 +3348,7 @@
     </row>
     <row r="25" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>62</v>
@@ -3537,16 +3360,16 @@
         <v>55</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>72</v>
@@ -3557,28 +3380,28 @@
     </row>
     <row r="26" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>55</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>59</v>
@@ -3589,28 +3412,28 @@
     </row>
     <row r="27" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>66</v>
@@ -3621,7 +3444,7 @@
     </row>
     <row r="28" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>69</v>
@@ -3633,16 +3456,16 @@
         <v>67</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>59</v>
@@ -3653,28 +3476,28 @@
     </row>
     <row r="29" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>72</v>
@@ -3685,28 +3508,28 @@
     </row>
     <row r="30" spans="1:10" ht="51" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>78</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>57</v>
@@ -3717,28 +3540,28 @@
     </row>
     <row r="31" spans="1:10" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>509</v>
+        <v>440</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>502</v>
+        <v>433</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>78</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>503</v>
+        <v>434</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>504</v>
+        <v>435</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>505</v>
+        <v>436</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>57</v>
@@ -3771,154 +3594,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="23" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="B5" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="23" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>545</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>546</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>548</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>549</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="B6" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>551</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>552</v>
-      </c>
-      <c r="D5" s="24" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="B7" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>553</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>552</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="B8" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="24" t="s">
-        <v>554</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>555</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+      <c r="B9" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>489</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B8" s="24" t="s">
-        <v>557</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>559</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>560</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>562</v>
+      <c r="B10" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="24" t="s">
-        <v>563</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>564</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>565</v>
+      <c r="B11" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -3942,26 +3765,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
+      <c r="A1" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>213</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>87</v>
@@ -3969,342 +3792,342 @@
     </row>
     <row r="3" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="E18" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4317,7 +4140,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4331,28 +4154,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>280</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>26</v>
@@ -4360,27 +4183,27 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B7" s="2">
-        <f>COUNTA(A15:A48)-1</f>
-        <v>26</v>
+        <f>COUNTA(A15:A47)-1</f>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -4388,40 +4211,40 @@
         <v>93</v>
       </c>
       <c r="B8" s="2">
-        <f>COUNTIF(F15:F48,"Pass")</f>
-        <v>21</v>
+        <f>COUNTIF(F15:F47,"Pass")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B9" s="2">
-        <f>COUNTIF(F15:F48,"Fail")</f>
+        <f>COUNTIF(F15:F47,"Fail")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B10" s="2">
-        <f>COUNTIF(F15:F48,"Blocked")</f>
+        <f>COUNTIF(F15:F47,"Blocked")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B11" s="2">
-        <f>COUNTIF(F15:F48,"Not Implemented")</f>
-        <v>2</v>
+        <f>COUNTIF(F15:F47,"Not Implemented")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B12" s="11" t="e">
         <f>IF(B20&gt;0,B21/B20,0)</f>
@@ -4436,22 +4259,22 @@
         <v>83</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -4465,16 +4288,16 @@
         <v>37</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>80</v>
@@ -4491,16 +4314,16 @@
         <v>37</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>80</v>
@@ -4517,16 +4340,16 @@
         <v>37</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>80</v>
@@ -4543,16 +4366,16 @@
         <v>37</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>80</v>
@@ -4569,16 +4392,16 @@
         <v>37</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>80</v>
@@ -4595,16 +4418,16 @@
         <v>37</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>80</v>
@@ -4621,16 +4444,16 @@
         <v>37</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>80</v>
@@ -4647,512 +4470,484 @@
         <v>37</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>93</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="5" t="s">
+    <row r="23" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>80</v>
+      <c r="D23" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="6" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>302</v>
+        <v>505</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>308</v>
+      <c r="H24" s="5" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>302</v>
+      <c r="D25" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>80</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>302</v>
+        <v>505</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>80</v>
       </c>
       <c r="H26" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>432</v>
-      </c>
-      <c r="G27" s="5" t="s">
+      <c r="F27" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H27" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C28" s="6" t="s">
+    </row>
+    <row r="28" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>313</v>
+      <c r="D28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H28" s="6" t="s">
+      <c r="G28" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H28" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="A29" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>313</v>
+      <c r="D29" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H29" s="5" t="s">
+      <c r="G29" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="6" t="s">
+      <c r="A30" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>313</v>
+      <c r="D30" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H30" s="6" t="s">
+      <c r="G30" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="A31" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>313</v>
+      <c r="D31" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="G31" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="A32" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>313</v>
+      <c r="D32" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H32" s="6" t="s">
+      <c r="G32" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H32" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>313</v>
+      <c r="D33" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H33" s="5" t="s">
+      <c r="G33" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>313</v>
+      <c r="D34" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>308</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H34" s="6" t="s">
+      <c r="G34" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="H34" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="A35" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>313</v>
+      <c r="D35" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="H35" s="5" t="s">
+      <c r="G35" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="3" t="s">
+    <row r="36" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="H36" s="6" t="s">
+      <c r="G36" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="A37" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>320</v>
+      <c r="D37" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>315</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="H37" s="5" t="s">
+      <c r="G37" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="H37" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>320</v>
+      <c r="D38" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>315</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>320</v>
+      <c r="E39" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H39" s="5" t="s">
+      <c r="G39" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="H39" s="6" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="40" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="B40" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="H40" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5166,7 +4961,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5179,38 +4974,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="A1" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>87</v>
@@ -5218,341 +5013,110 @@
     </row>
     <row r="3" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>115</v>
+        <v>446</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>334</v>
+        <v>499</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>337</v>
+        <v>502</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>38</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>115</v>
+        <v>447</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>340</v>
+        <v>498</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>38</v>
       </c>
       <c r="H4" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>347</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>38</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>437</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="D7" s="19" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="G7" s="19" t="s">
+      <c r="C6" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>453</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>457</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>459</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>468</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>475</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>480</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>338</v>
-      </c>
+      <c r="H6" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5572,22 +5136,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="B1" s="26"/>
+      <c r="A1" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="B1" s="25"/>
     </row>
     <row r="2" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>26</v>
@@ -5595,234 +5159,234 @@
     </row>
     <row r="4" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B6" s="14"/>
     </row>
     <row r="7" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B15" s="14"/>
     </row>
     <row r="16" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B32" s="14"/>
     </row>
     <row r="33" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5830,7 +5394,7 @@
         <v>68</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5838,7 +5402,7 @@
         <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5846,145 +5410,145 @@
         <v>50</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B40" s="14"/>
     </row>
     <row r="41" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B46" s="14"/>
     </row>
     <row r="47" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B53" s="14"/>
     </row>
     <row r="54" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
